--- a/type21/json.xlsx
+++ b/type21/json.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>list1</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -272,12 +272,92 @@
     <t>序号</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>《推拿手法治疗幼儿脾胃病》</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>《推拿手法治疗小儿鼻渊》</t>
+  </si>
+  <si>
+    <t>《小儿推拿治疗哮病》</t>
+  </si>
+  <si>
+    <t>《小儿推拿治疗感冒》</t>
+  </si>
+  <si>
+    <t>《推拿治疗小儿肌性斜颈》</t>
+  </si>
+  <si>
+    <t>《推拿治疗小儿鼾证》</t>
+  </si>
+  <si>
+    <t>《小儿夜啼的推拿治疗》</t>
+  </si>
+  <si>
+    <t>《推拿治疗小儿厌食》</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>《小儿推拿治惊风》</t>
+  </si>
+  <si>
+    <t>《小儿推拿治泄泻》</t>
+  </si>
+  <si>
+    <t>《小儿推拿治便秘》</t>
+  </si>
+  <si>
+    <t>《推拿治疗小儿遗尿》</t>
+  </si>
+  <si>
+    <t>《小儿推拿治疗脱肛》</t>
+  </si>
+  <si>
+    <t>list16</t>
+  </si>
+  <si>
+    <t>list17</t>
+  </si>
+  <si>
+    <t>list18</t>
+  </si>
+  <si>
+    <t>list19</t>
+  </si>
+  <si>
+    <t>list20</t>
+  </si>
+  <si>
+    <t>list21</t>
+  </si>
+  <si>
+    <t>list22</t>
+  </si>
+  <si>
+    <t>list23</t>
+  </si>
+  <si>
+    <t>list24</t>
+  </si>
+  <si>
+    <t>list25</t>
+  </si>
+  <si>
+    <t>list26</t>
+  </si>
+  <si>
+    <t>list27</t>
+  </si>
+  <si>
+    <t>list28</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -297,6 +377,12 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -324,11 +410,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -910,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
@@ -1089,13 +1178,153 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B17" s="1"/>
+    <row r="17" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
+      <c r="A17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="1">
+        <v>3</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
+      <c r="A18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="1">
+        <v>3</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
+      <c r="A19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="1">
+        <v>3</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
+      <c r="A20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="1">
+        <v>3</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
+      <c r="A21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="1">
+        <v>3</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
+      <c r="A22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="1">
+        <v>3</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
+      <c r="A23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="1">
+        <v>3</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
+      <c r="A24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="1">
+        <v>3</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
+      <c r="A25" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="1">
+        <v>3</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
+      <c r="A26" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" s="1">
+        <v>3</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
+      <c r="A27" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="1">
+        <v>3</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
+      <c r="A28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="1">
+        <v>3</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
+      <c r="A29" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="1">
+        <v>3</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter scaleWithDoc="0" alignWithMargins="0"/>
 </worksheet>
 </file>

--- a/type21/json.xlsx
+++ b/type21/json.xlsx
@@ -261,10 +261,6 @@
     <t>list15</t>
   </si>
   <si>
-    <t>字号</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>内容</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -351,6 +347,10 @@
   </si>
   <si>
     <t>list28</t>
+  </si>
+  <si>
+    <t>类别</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1004,13 +1004,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
@@ -1018,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="1">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>8</v>
@@ -1029,7 +1029,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
@@ -1040,7 +1040,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>10</v>
@@ -1051,7 +1051,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1">
-        <v>3</v>
+        <v>201</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
@@ -1062,7 +1062,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1">
-        <v>3</v>
+        <v>202</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>12</v>
@@ -1073,7 +1073,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>13</v>
@@ -1084,7 +1084,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="1">
-        <v>3</v>
+        <v>301</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
@@ -1095,7 +1095,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="1">
-        <v>3</v>
+        <v>302</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>15</v>
@@ -1106,7 +1106,7 @@
         <v>23</v>
       </c>
       <c r="B10" s="1">
-        <v>3</v>
+        <v>303</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>16</v>
@@ -1117,7 +1117,7 @@
         <v>24</v>
       </c>
       <c r="B11" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>17</v>
@@ -1128,7 +1128,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="1">
-        <v>3</v>
+        <v>401</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>18</v>
@@ -1139,7 +1139,7 @@
         <v>26</v>
       </c>
       <c r="B13" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>19</v>
@@ -1150,7 +1150,7 @@
         <v>27</v>
       </c>
       <c r="B14" s="1">
-        <v>3</v>
+        <v>501</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>20</v>
@@ -1161,7 +1161,7 @@
         <v>28</v>
       </c>
       <c r="B15" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>21</v>
@@ -1172,7 +1172,7 @@
         <v>29</v>
       </c>
       <c r="B16" s="1">
-        <v>3</v>
+        <v>601</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>22</v>
@@ -1180,145 +1180,145 @@
     </row>
     <row r="17" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" s="1">
-        <v>3</v>
+        <v>602</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" s="1">
-        <v>3</v>
+        <v>603</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1">
-        <v>3</v>
+        <v>604</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20" s="1">
-        <v>3</v>
+        <v>605</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B21" s="1">
-        <v>3</v>
+        <v>606</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B22" s="1">
-        <v>3</v>
+        <v>607</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B23" s="1">
-        <v>3</v>
+        <v>608</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B24" s="1">
-        <v>3</v>
+        <v>609</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B25" s="1">
-        <v>3</v>
+        <v>610</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B26" s="1">
-        <v>3</v>
+        <v>611</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B27" s="1">
-        <v>3</v>
+        <v>612</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B28" s="1">
-        <v>3</v>
+        <v>613</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B29" s="1">
-        <v>3</v>
+        <v>614</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/type21/json.xlsx
+++ b/type21/json.xlsx
@@ -168,10 +168,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>针对小儿反复感冒这一临床难点，创新性提出“节气治肺”和“病后调护”结合的系统防治方案</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>著作</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -350,6 +346,10 @@
   </si>
   <si>
     <t>类别</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对小儿反复感冒这一临床难点，创新性提出【节气治肺】和【病后调护】结合的系统防治方案</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1004,13 +1004,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10" s="1">
         <v>303</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" s="1">
         <v>4</v>
@@ -1125,7 +1125,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" s="1">
         <v>401</v>
@@ -1136,7 +1136,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B13" s="1">
         <v>5</v>
@@ -1147,178 +1147,178 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B14" s="1">
         <v>501</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1">
         <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B16" s="1">
         <v>601</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1">
         <v>602</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1">
         <v>603</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19" s="1">
         <v>604</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1">
         <v>605</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B21" s="1">
         <v>606</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B22" s="1">
         <v>607</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B23" s="1">
         <v>608</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B24" s="1">
         <v>609</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B25" s="1">
         <v>610</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B26" s="1">
         <v>611</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B27" s="1">
         <v>612</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B28" s="1">
         <v>613</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B29" s="1">
         <v>614</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
